--- a/astro-site/public/dl/guia-restaurante-gastronomico/pl-mensual-escenarios.xlsx
+++ b/astro-site/public/dl/guia-restaurante-gastronomico/pl-mensual-escenarios.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escenarios" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Escenarios'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -486,9 +488,9 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -508,6 +510,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -536,10 +539,19 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Celdas verdes = campos editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/guia-restaurante-gastronomico · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -548,7 +560,16 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -556,7 +577,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -582,6 +603,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -781,6 +803,15 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/guia-restaurante-gastronomico/pl-mensual-escenarios.xlsx
+++ b/astro-site/public/dl/guia-restaurante-gastronomico/pl-mensual-escenarios.xlsx
@@ -19,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +59,21 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +90,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="002D2D2D"/>
         <bgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -124,10 +143,60 @@
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -490,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -541,7 +610,7 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Celdas verdes = campos editables</t>
         </is>
@@ -549,13 +618,35 @@
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/guia-restaurante-gastronomico · info@aichef.pro</t>
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Todas las cifras van SIN IVA. En el cash flow también se escriben sin IVA: su capa de IVA (modelo 303) lo añade aparte, porque la tesorería es caja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Para editar la estructura o una celda que no esté en verde: Revisar → Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/guia-restaurante-gastronomico · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:C1"/>
@@ -579,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -603,7 +694,13 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Todas las cifras van SIN IVA. En el cash flow también se escriben sin IVA: su capa de IVA (modelo 303) lo añade aparte, porque la tesorería es caja.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -644,9 +741,15 @@
           <t>Cubiertos/día comida</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n"/>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
+      <c r="B6" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -654,9 +757,15 @@
           <t>Cubiertos/día cena</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
+      <c r="B7" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -664,9 +773,15 @@
           <t>Ticket medio comida (€)</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
+      <c r="B8" s="14" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>88.91</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>98.25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -674,9 +789,15 @@
           <t>Ticket medio cena (€)</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
+      <c r="B9" s="14" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>142.25</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>157.14</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -684,9 +805,15 @@
           <t>Días abierto/mes</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
+      <c r="B10" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -694,9 +821,20 @@
           <t>Food cost (%)</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
+      <c r="B11" s="15" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>Capítulo 3: 25‑28 % en el modelo de solo menú degustación y 28‑32 % en el de carta + menú.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -704,9 +842,20 @@
           <t>Coste personal mensual (€)</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
+      <c r="B12" s="14" t="n">
+        <v>47000</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>59801.68</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>78000</v>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>Coste con la SS de la empresa YA incluida (33 %, la celda C41 de plantilla-turnos-brigada.xlsx). Los rangos del capítulo 13 —cocina 250.000‑450.000 €/año y sala 200.000‑350.000 €— son BRUTOS, sin SS: con el 33 % son cocina 322.400‑601.900 € y sala 234.000‑403.000 €, o 556 k€-1,0 M€ en total. Los tres escenarios (564 / 718 / 936 k€ al año) caben ahí. El realista NO se teclea: es el coste de la brigada de plantilla-turnos-brigada.xlsx.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -714,9 +863,20 @@
           <t>Alquiler mensual (€)</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
+      <c r="B13" s="14" t="n">
+        <v>17000</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>17000</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>El alquiler es FIJO: no baja porque vendas menos. En el escenario realista son el 9,0 % de la facturación, dentro del 8‑12 % de zona premium del capítulo 8; en el pesimista pesan el 12,9 %, y eso es exactamente lo que significa un escenario malo.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -724,9 +884,20 @@
           <t>Otros costes fijos mensuales (€)</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
+      <c r="B14" s="14" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>22000</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>26000</v>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>Suministros, seguros, marketing, tecnología, mantenimiento, limpieza y gestoría. La amortización va en su PROPIA fila, debajo: si entrase aquí, el «EBITDA» sería un EBIT. Parametrizado: sustitúyelo por tu presupuesto real.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr"/>
@@ -744,9 +915,18 @@
           <t>Facturación mensual (€)</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
+      <c r="B17" s="17">
+        <f>(B6*B8+B7*B9)*B10</f>
+        <v>131736.0</v>
+      </c>
+      <c r="C17" s="17">
+        <f>(C6*C8+C7*C9)*C10</f>
+        <v>189728.0</v>
+      </c>
+      <c r="D17" s="17">
+        <f>(D6*D8+D7*D9)*D10</f>
+        <v>233376.0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -754,9 +934,18 @@
           <t>Coste materia prima (€)</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
+      <c r="B18" s="17">
+        <f>B17*B11</f>
+        <v>42155.520000000004</v>
+      </c>
+      <c r="C18" s="17">
+        <f>C17*C11</f>
+        <v>56918.4</v>
+      </c>
+      <c r="D18" s="17">
+        <f>D17*D11</f>
+        <v>65345.280000000006</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -764,9 +953,18 @@
           <t>Margen bruto (€)</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
+      <c r="B19" s="17">
+        <f>B17-B18</f>
+        <v>89580.48</v>
+      </c>
+      <c r="C19" s="17">
+        <f>C17-C18</f>
+        <v>132809.6</v>
+      </c>
+      <c r="D19" s="17">
+        <f>D17-D18</f>
+        <v>168030.72</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -774,9 +972,18 @@
           <t>Costes fijos totales (€)</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
+      <c r="B20" s="17">
+        <f>SUM(B12:B14)</f>
+        <v>86000.0</v>
+      </c>
+      <c r="C20" s="17">
+        <f>SUM(C12:C14)</f>
+        <v>98801.68</v>
+      </c>
+      <c r="D20" s="17">
+        <f>SUM(D12:D14)</f>
+        <v>121000.0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -784,9 +991,18 @@
           <t>EBITDA mensual (€)</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
+      <c r="B21" s="18">
+        <f>B19-B20</f>
+        <v>3580.479999999996</v>
+      </c>
+      <c r="C21" s="18">
+        <f>C19-C20</f>
+        <v>34007.92000000001</v>
+      </c>
+      <c r="D21" s="18">
+        <f>D19-D20</f>
+        <v>47030.72</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -794,15 +1010,89 @@
           <t>Margen EBITDA (%)</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
+      <c r="B22" s="19">
+        <f>IF(B17=0,"",B21/B17)</f>
+        <v>0.027179206898645746</v>
+      </c>
+      <c r="C22" s="19">
+        <f>IF(C17=0,"",C21/C17)</f>
+        <v>0.1792456569404622</v>
+      </c>
+      <c r="D22" s="19">
+        <f>IF(D17=0,"",D21/D17)</f>
+        <v>0.20152337858220212</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Amortización mensual (€)</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C23" s="20" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D23" s="20" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>Amortización mensual del equipamiento y la obra. NO resta del EBITDA (por eso está debajo): resta del EBIT, que es la fila siguiente. Parametrizado: divide tu CAPEX amortizable entre los años de vida útil y entre 12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EBIT — resultado de explotación (€)</t>
+        </is>
+      </c>
+      <c r="B24" s="21">
+        <f>IF(B21="","",B21-IF(ISNUMBER(B23),B23,0))</f>
+        <v>-2419.520000000004</v>
+      </c>
+      <c r="C24" s="21">
+        <f>IF(C21="","",C21-IF(ISNUMBER(C23),C23,0))</f>
+        <v>28007.920000000013</v>
+      </c>
+      <c r="D24" s="21">
+        <f>IF(D21="","",D21-IF(ISNUMBER(D23),D23,0))</f>
+        <v>41030.72</v>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
+  <conditionalFormatting sqref="B21:D21">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>=AND(ISNUMBER(B21),B21&lt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22:D22">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+      <formula>=AND(ISNUMBER(B22),B22&lt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24:D24">
+    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="1">
+      <formula>=AND(ISNUMBER(B24),B24&lt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B12 B13 B14 B23 C6 C7 C8 C9 C10 C12 C13 C14 C23 D6 D7 D8 D9 D10 D12 D13 D14 D23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B11 C11 D11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Porcentaje" error="Escribe un porcentaje entre 0 y 1 (0,20 = 20 %)." promptTitle="Porcentaje" prompt="Se escribe en tanto por uno: 0,20 = 20 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1.0</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>

--- a/astro-site/public/dl/guia-restaurante-gastronomico/pl-mensual-escenarios.xlsx
+++ b/astro-site/public/dl/guia-restaurante-gastronomico/pl-mensual-escenarios.xlsx
@@ -1070,12 +1070,12 @@
     <mergeCell ref="A2:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="B21:D21">
-    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="1">
       <formula>=AND(ISNUMBER(B21),B21&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:D22">
-    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="1">
       <formula>=AND(ISNUMBER(B22),B22&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
